--- a/LAPORAN STOK/DATA STOK DVR.xlsx
+++ b/LAPORAN STOK/DATA STOK DVR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\LAPORAN STOK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910586D-87A7-4BCA-AD01-07FE08528EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A628DE38-D0A4-4138-AC73-9A2AC52FDCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A8B0BE85-9D20-4728-AB63-3A1F33C5DAD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Nama Barang</t>
   </si>
@@ -78,12 +78,27 @@
   </si>
   <si>
     <t>Dvr Proview 16ch</t>
+  </si>
+  <si>
+    <t>Harga</t>
+  </si>
+  <si>
+    <t>Ezviz H6c Pro 2k</t>
+  </si>
+  <si>
+    <t>Ezviz H6c Pro 2k + Memory 32GB</t>
+  </si>
+  <si>
+    <t>Ezviz H6c Pro 2k + Memory 64GB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0.00_-;\-[$Rp-421]* #,##0.00_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -218,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -251,6 +266,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F4F587-1884-41DC-8C6A-A0720FB29EF8}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -593,17 +609,21 @@
     <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="9.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>0</v>
@@ -619,8 +639,14 @@
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="5" t="s">
         <v>3</v>
@@ -636,8 +662,14 @@
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="14">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="5" t="s">
         <v>4</v>
@@ -653,8 +685,14 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="14">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
         <v>5</v>
@@ -670,8 +708,14 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="14">
+        <v>675000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="6" t="s">
         <v>6</v>
@@ -687,8 +731,10 @@
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K7" s="6"/>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="6" t="s">
         <v>7</v>
@@ -704,8 +750,10 @@
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K8" s="6"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="6" t="s">
         <v>8</v>
@@ -721,8 +769,10 @@
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K9" s="6"/>
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="6" t="s">
         <v>2</v>
@@ -738,8 +788,10 @@
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K10" s="6"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="6" t="s">
         <v>12</v>
@@ -755,8 +807,10 @@
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K11" s="6"/>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="6" t="s">
         <v>13</v>
@@ -772,8 +826,10 @@
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K12" s="6"/>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -781,8 +837,10 @@
       <c r="E13" s="10"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="K13" s="6"/>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -791,7 +849,7 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -800,7 +858,7 @@
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
